--- a/test_data/RegBriefings/RegBriefings Transfer Pricing Brief/RegBriefings Transfer Pricing Brief_Test_Cases.xlsx
+++ b/test_data/RegBriefings/RegBriefings Transfer Pricing Brief/RegBriefings Transfer Pricing Brief_Test_Cases.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Transfer Pricing Brief correctly shows 8 real country entries (10 with 'Full Story' links on this environment).</t>
+          <t>Transfer Pricing Brief correctly shows 12 real country entries (15 with 'Full Story' links on this environment).</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Search correctly filtered from 8 to 1 entries, keeping 'Australia' visible.</t>
+          <t>Search correctly filtered from 12 to 1 entries, keeping 'Australia' visible.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Clearing the search box correctly restored all 8 entries.</t>
+          <t>Clearing the search box correctly restored all 12 entries.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
